--- a/nriss-patch-1/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:10:58+00:00</t>
+    <t>2024-06-05T12:12:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:38:14+00:00</t>
+    <t>2026-06-30T07:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
